--- a/artfynd/A 33057-2022 artfynd.xlsx
+++ b/artfynd/A 33057-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33057-2022 artfynd.xlsx
+++ b/artfynd/A 33057-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106820291</v>
+        <v>106820059</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558345.6345782836</v>
+        <v>558361</v>
       </c>
       <c r="R2" t="n">
-        <v>6270260.692764896</v>
+        <v>6270226</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106819409</v>
+        <v>106820291</v>
       </c>
       <c r="B3" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558247.8168052527</v>
+        <v>558346</v>
       </c>
       <c r="R3" t="n">
-        <v>6270268.705842937</v>
+        <v>6270261</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106819345</v>
+        <v>106820408</v>
       </c>
       <c r="B4" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558268.9720501025</v>
+        <v>558421</v>
       </c>
       <c r="R4" t="n">
-        <v>6270255.776690409</v>
+        <v>6270262</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106820471</v>
+        <v>106819345</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +980,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558532.7327646136</v>
+        <v>558269</v>
       </c>
       <c r="R5" t="n">
-        <v>6270263.285192795</v>
+        <v>6270256</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106820408</v>
+        <v>106819409</v>
       </c>
       <c r="B6" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558421.7984495664</v>
+        <v>558248</v>
       </c>
       <c r="R6" t="n">
-        <v>6270261.747087762</v>
+        <v>6270269</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2023-02-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,6 +1162,104 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>106820471</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sandbäckskärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>558533</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6270263</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33057-2022 artfynd.xlsx
+++ b/artfynd/A 33057-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106820059</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106820291</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106820408</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106819345</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106819409</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,8 +1290,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106820471</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>